--- a/calculadoras excel/Simulador GI Real.xlsx
+++ b/calculadoras excel/Simulador GI Real.xlsx
@@ -988,10 +988,10 @@
         <v/>
       </c>
       <c r="G11" s="19" t="n">
-        <v>912.7</v>
+        <v>924.7</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>917.7</v>
+        <v>929.7</v>
       </c>
       <c r="I11" s="20" t="n">
         <v>2</v>
@@ -1043,10 +1043,10 @@
         <v/>
       </c>
       <c r="G12" s="19" t="n">
-        <v>919.7</v>
+        <v>931.7</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>916.7</v>
+        <v>928.7</v>
       </c>
       <c r="I12" s="20" t="n">
         <v>1</v>
@@ -1098,10 +1098,10 @@
         <v/>
       </c>
       <c r="G13" s="19" t="n">
-        <v>915.7</v>
+        <v>927.7</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>914.2</v>
+        <v>926.2</v>
       </c>
       <c r="I13" s="20" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
     <row r="27" ht="42" customHeight="1">
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>Especificaciones de la cuenta real del broker al 2026-08-24 10:45 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos del paso que acepta MT5 en ese instrumento, indicado arriba a la derecha. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker avisa cuando el nivel de margen baja de 200% y cierra posiciones por su cuenta en 50%, que es el umbral contra el que se mide el recorrido. Este simulador no incorpora stop loss.</t>
+          <t>Especificaciones de la cuenta real del broker al 2026-09-09 15:08 hora Chile. Celdas crema: campos editables; el resto son fórmulas. El volumen en lotes se escribe en múltiplos del paso que acepta MT5 en ese instrumento, indicado arriba a la derecha. APALANCAMIENTO son las veces que el capital de la cuenta queda controlado por esa operación, y la columna es aditiva: su total es el apalancamiento del periodo. El COSTO DE MANTENCIÓN (SWAP) se estima por días calendario. El broker avisa cuando el nivel de margen baja de 200% y cierra posiciones por su cuenta en 50%, que es el umbral contra el que se mide el recorrido. Este simulador no incorpora stop loss.</t>
         </is>
       </c>
       <c r="D27" s="32" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>100000</v>
       </c>
       <c r="E2" t="n">
-        <v>66210656.47</v>
+        <v>67222202.09</v>
       </c>
       <c r="F2" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -1584,7 +1584,7 @@
         <v>0.0004</v>
       </c>
       <c r="H2" s="35" t="n">
-        <v>0.99028</v>
+        <v>0.99701</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1625,7 +1625,7 @@
         <v>100000</v>
       </c>
       <c r="E3" t="n">
-        <v>575524.65</v>
+        <v>604431.76</v>
       </c>
       <c r="F3" s="34" t="n">
         <v>0.009998</v>
@@ -1634,7 +1634,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>113.939</v>
+        <v>110.898</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1675,7 +1675,7 @@
         <v>100000</v>
       </c>
       <c r="E4" t="n">
-        <v>54626999.2</v>
+        <v>54227775.8</v>
       </c>
       <c r="F4" s="34" t="n">
         <v>0.009996</v>
@@ -1684,7 +1684,7 @@
         <v>0.0006000000000000001</v>
       </c>
       <c r="H4" s="35" t="n">
-        <v>1.20072</v>
+        <v>1.23638</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1725,7 +1725,7 @@
         <v>100000</v>
       </c>
       <c r="E5" t="n">
-        <v>114182752.26</v>
+        <v>114625678.03</v>
       </c>
       <c r="F5" s="34" t="n">
         <v>0.009991</v>
@@ -1734,7 +1734,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>0.57468</v>
+        <v>0.5851499999999999</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>100000</v>
       </c>
       <c r="E6" t="n">
-        <v>91570000</v>
+        <v>92770000</v>
       </c>
       <c r="F6" s="34" t="n">
         <v>0.01</v>
@@ -1784,7 +1784,7 @@
         <v>0.00032</v>
       </c>
       <c r="H6" s="35" t="n">
-        <v>0.7159799999999999</v>
+        <v>0.72239</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1825,7 +1825,7 @@
         <v>100000</v>
       </c>
       <c r="E7" t="n">
-        <v>54626999.2</v>
+        <v>54227775.8</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>0.019982</v>
@@ -1834,7 +1834,7 @@
         <v>0.003</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>2.28905</v>
+        <v>2.32201</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>100000</v>
       </c>
       <c r="E8" t="n">
-        <v>65562288.6</v>
+        <v>67016120.3</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>0.009997000000000001</v>
@@ -1884,7 +1884,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H8" s="35" t="n">
-        <v>1.90609</v>
+        <v>1.87777</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1925,7 +1925,7 @@
         <v>100000</v>
       </c>
       <c r="E9" t="n">
-        <v>66210656.47</v>
+        <v>67222202.09</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>0.009998</v>
@@ -1934,7 +1934,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>1.88718</v>
+        <v>1.87178</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         <v>100000</v>
       </c>
       <c r="E10" t="n">
-        <v>575524.65</v>
+        <v>604431.76</v>
       </c>
       <c r="F10" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -1984,7 +1984,7 @@
         <v>0.08</v>
       </c>
       <c r="H10" s="35" t="n">
-        <v>217.1</v>
+        <v>208.164</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>100000</v>
       </c>
       <c r="E11" t="n">
-        <v>114182752.26</v>
+        <v>114625678.03</v>
       </c>
       <c r="F11" s="34" t="n">
         <v>0.009995</v>
@@ -2034,7 +2034,7 @@
         <v>0.0008</v>
       </c>
       <c r="H11" s="35" t="n">
-        <v>1.09467</v>
+        <v>1.09806</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2075,7 +2075,7 @@
         <v>100000</v>
       </c>
       <c r="E12" t="n">
-        <v>575524.65</v>
+        <v>604431.76</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>0.009998</v>
@@ -2084,7 +2084,7 @@
         <v>0.05</v>
       </c>
       <c r="H12" s="35" t="n">
-        <v>115.071</v>
+        <v>111.243</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2125,7 +2125,7 @@
         <v>100000</v>
       </c>
       <c r="E13" t="n">
-        <v>114182752.26</v>
+        <v>114625678.03</v>
       </c>
       <c r="F13" s="34" t="n">
         <v>0.009991</v>
@@ -2134,7 +2134,7 @@
         <v>0.00075</v>
       </c>
       <c r="H13" s="35" t="n">
-        <v>0.5803700000000001</v>
+        <v>0.58695</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2184,7 +2184,7 @@
         <v>0.4</v>
       </c>
       <c r="H14" s="35" t="n">
-        <v>915.7</v>
+        <v>927.7</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2225,16 +2225,16 @@
         <v>100000</v>
       </c>
       <c r="E15" t="n">
-        <v>571787.17</v>
+        <v>600363.7</v>
       </c>
       <c r="F15" s="34" t="n">
-        <v>0.010063</v>
+        <v>0.010065</v>
       </c>
       <c r="G15" s="35" t="n">
         <v>0.04</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>159.147</v>
+        <v>153.523</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
         <v>-2.513</v>
       </c>
       <c r="K15" t="n">
-        <v>-23.933</v>
+        <v>-18</v>
       </c>
       <c r="L15" t="n">
         <v>0.01</v>
@@ -2275,7 +2275,7 @@
         <v>100000</v>
       </c>
       <c r="E16" t="n">
-        <v>91570000</v>
+        <v>92770000</v>
       </c>
       <c r="F16" s="34" t="n">
         <v>0.01</v>
@@ -2284,7 +2284,7 @@
         <v>0.00026</v>
       </c>
       <c r="H16" s="35" t="n">
-        <v>1.16708</v>
+        <v>1.16395</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2325,7 +2325,7 @@
         <v>100000</v>
       </c>
       <c r="E17" t="n">
-        <v>65562288.6</v>
+        <v>67016120.3</v>
       </c>
       <c r="F17" s="34" t="n">
         <v>0.009997000000000001</v>
@@ -2334,7 +2334,7 @@
         <v>0.0006000000000000001</v>
       </c>
       <c r="H17" s="35" t="n">
-        <v>1.63055</v>
+        <v>1.61173</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2375,7 +2375,7 @@
         <v>100000</v>
       </c>
       <c r="E18" t="n">
-        <v>124932613.8</v>
+        <v>125805397</v>
       </c>
       <c r="F18" s="34" t="n">
         <v>0.009996</v>
@@ -2384,7 +2384,7 @@
         <v>0.0005</v>
       </c>
       <c r="H18" s="35" t="n">
-        <v>0.85573</v>
+        <v>0.85862</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2425,7 +2425,7 @@
         <v>100000</v>
       </c>
       <c r="E19" t="n">
-        <v>66210656.47</v>
+        <v>67222202.09</v>
       </c>
       <c r="F19" s="34" t="n">
         <v>0.009997000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H19" s="35" t="n">
-        <v>1.61451</v>
+        <v>1.60673</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2475,7 +2475,7 @@
         <v>100000</v>
       </c>
       <c r="E20" t="n">
-        <v>575524.65</v>
+        <v>604431.76</v>
       </c>
       <c r="F20" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -2484,7 +2484,7 @@
         <v>0.05</v>
       </c>
       <c r="H20" s="35" t="n">
-        <v>185.716</v>
+        <v>178.673</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2525,7 +2525,7 @@
         <v>100000</v>
       </c>
       <c r="E21" t="n">
-        <v>54626999.2</v>
+        <v>54227775.8</v>
       </c>
       <c r="F21" s="34" t="n">
         <v>0.009995</v>
@@ -2534,7 +2534,7 @@
         <v>0.0009000000000000001</v>
       </c>
       <c r="H21" s="35" t="n">
-        <v>1.95741</v>
+        <v>1.99229</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2575,16 +2575,16 @@
         <v>100000</v>
       </c>
       <c r="E22" t="n">
-        <v>114182752.26</v>
+        <v>114625678.03</v>
       </c>
       <c r="F22" s="34" t="n">
-        <v>0.009995</v>
+        <v>0.009996</v>
       </c>
       <c r="G22" s="35" t="n">
         <v>0.0005</v>
       </c>
       <c r="H22" s="35" t="n">
-        <v>0.9363899999999999</v>
+        <v>0.9424400000000001</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2625,7 +2625,7 @@
         <v>100000</v>
       </c>
       <c r="E23" t="n">
-        <v>1907662.63</v>
+        <v>1916960.11</v>
       </c>
       <c r="F23" s="34" t="n">
         <v>0.009967999999999999</v>
@@ -2634,7 +2634,7 @@
         <v>0.1</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>56.19975</v>
+        <v>56.50814</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>100000</v>
       </c>
       <c r="E24" t="n">
-        <v>91570000</v>
+        <v>92770000</v>
       </c>
       <c r="F24" s="34" t="n">
         <v>0.01</v>
@@ -2684,7 +2684,7 @@
         <v>0.0005</v>
       </c>
       <c r="H24" s="35" t="n">
-        <v>1.36434</v>
+        <v>1.3561</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2725,7 +2725,7 @@
         <v>100000</v>
       </c>
       <c r="E25" t="n">
-        <v>66210656.47</v>
+        <v>67222202.09</v>
       </c>
       <c r="F25" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -2734,7 +2734,7 @@
         <v>0.00075</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>0.82517</v>
+        <v>0.80681</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -2775,7 +2775,7 @@
         <v>100000</v>
       </c>
       <c r="E26" t="n">
-        <v>575524.65</v>
+        <v>604431.76</v>
       </c>
       <c r="F26" s="34" t="n">
         <v>0.009998999999999999</v>
@@ -2784,7 +2784,7 @@
         <v>0.075</v>
       </c>
       <c r="H26" s="35" t="n">
-        <v>94.926</v>
+        <v>89.72799999999999</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -2825,7 +2825,7 @@
         <v>100000</v>
       </c>
       <c r="E27" t="n">
-        <v>114182752.26</v>
+        <v>114625678.03</v>
       </c>
       <c r="F27" s="34" t="n">
         <v>0.009993</v>
@@ -2834,7 +2834,7 @@
         <v>0.00075</v>
       </c>
       <c r="H27" s="35" t="n">
-        <v>0.47875</v>
+        <v>0.47341</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -2875,7 +2875,7 @@
         <v>100000</v>
       </c>
       <c r="E28" t="n">
-        <v>91570000</v>
+        <v>92770000</v>
       </c>
       <c r="F28" s="34" t="n">
         <v>0.01</v>
@@ -2884,7 +2884,7 @@
         <v>0.0005</v>
       </c>
       <c r="H28" s="35" t="n">
-        <v>0.59656</v>
+        <v>0.5845399999999999</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         <v>100000</v>
       </c>
       <c r="E29" t="n">
-        <v>575524.65</v>
+        <v>604431.76</v>
       </c>
       <c r="F29" s="34" t="n">
         <v>0.01</v>
@@ -2934,7 +2934,7 @@
         <v>0.075</v>
       </c>
       <c r="H29" s="35" t="n">
-        <v>198.399</v>
+        <v>189.646</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -2975,16 +2975,16 @@
         <v>100000</v>
       </c>
       <c r="E30" t="n">
-        <v>38419420.75</v>
+        <v>38971295.58</v>
       </c>
       <c r="F30" s="34" t="n">
-        <v>0.017228</v>
+        <v>0.017244</v>
       </c>
       <c r="G30" s="35" t="n">
         <v>0.00042</v>
       </c>
       <c r="H30" s="35" t="n">
-        <v>1.38343</v>
+        <v>1.38047</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -3025,16 +3025,16 @@
         <v>100000</v>
       </c>
       <c r="E31" t="n">
-        <v>5099801.73</v>
+        <v>5184651.15</v>
       </c>
       <c r="F31" s="34" t="n">
-        <v>0.01059</v>
+        <v>0.010592</v>
       </c>
       <c r="G31" s="35" t="n">
         <v>0.008</v>
       </c>
       <c r="H31" s="35" t="n">
-        <v>16.9556</v>
+        <v>16.8932</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -3075,16 +3075,16 @@
         <v>100000</v>
       </c>
       <c r="E32" t="n">
-        <v>50802791.74</v>
+        <v>51258958.02</v>
       </c>
       <c r="F32" s="34" t="n">
-        <v>0.022462</v>
+        <v>0.022348</v>
       </c>
       <c r="G32" s="35" t="n">
         <v>0.0005</v>
       </c>
       <c r="H32" s="35" t="n">
-        <v>0.80246</v>
+        <v>0.80983</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -3125,16 +3125,16 @@
         <v>100000</v>
       </c>
       <c r="E33" t="n">
-        <v>1862649.67</v>
+        <v>1872086.66</v>
       </c>
       <c r="F33" s="34" t="n">
-        <v>0.163322</v>
+        <v>0.163295</v>
       </c>
       <c r="G33" s="35" t="n">
         <v>0.16</v>
       </c>
       <c r="H33" s="35" t="n">
-        <v>48.16115</v>
+        <v>48.55433</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -3175,7 +3175,7 @@
         <v>10000</v>
       </c>
       <c r="E34" t="n">
-        <v>9153000</v>
+        <v>9273000</v>
       </c>
       <c r="F34" s="34" t="n">
         <v>0.010004</v>
@@ -3184,7 +3184,7 @@
         <v>0.01</v>
       </c>
       <c r="H34" s="35" t="n">
-        <v>2.868</v>
+        <v>2.903</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -3225,22 +3225,22 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>91530</v>
+        <v>92730</v>
       </c>
       <c r="F35" s="34" t="n">
-        <v>0.04502</v>
+        <v>0.045019</v>
       </c>
       <c r="G35" s="35" t="n">
         <v>0.6</v>
       </c>
       <c r="H35" s="35" t="n">
-        <v>4672.63</v>
+        <v>4416.97</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>-16</v>
+        <v>-64</v>
       </c>
       <c r="K35" t="n">
         <v>-6</v>
@@ -3260,12 +3260,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Petróleo WTI</t>
+          <t>Petróleo Brent</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WTI.spot</t>
+          <t>BRENT.spot</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3275,16 +3275,16 @@
         <v>100</v>
       </c>
       <c r="E36" t="n">
-        <v>91530</v>
+        <v>92730</v>
       </c>
       <c r="F36" s="34" t="n">
-        <v>0.015007</v>
+        <v>0.015006</v>
       </c>
       <c r="G36" s="35" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H36" s="35" t="n">
-        <v>85.64700000000001</v>
+        <v>102.269</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -3310,40 +3310,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Plata</t>
+          <t>Petróleo WTI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XAGUSD</t>
+          <t>WTI.spot</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="E37" t="n">
-        <v>4576500</v>
+        <v>92730</v>
       </c>
       <c r="F37" s="34" t="n">
-        <v>0.04502</v>
+        <v>0.015006</v>
       </c>
       <c r="G37" s="35" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H37" s="35" t="n">
-        <v>69.063</v>
+        <v>96.346</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="K37" t="n">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="L37" t="n">
         <v>0.01</v>
@@ -3360,40 +3360,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UK Oil</t>
+          <t>Plata</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BRENT.spot</t>
+          <t>XAGUSD</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="E38" t="n">
-        <v>91530</v>
+        <v>4636500</v>
       </c>
       <c r="F38" s="34" t="n">
-        <v>0.015007</v>
+        <v>0.045019</v>
       </c>
       <c r="G38" s="35" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H38" s="35" t="n">
-        <v>92.76600000000001</v>
+        <v>67.869</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="K38" t="n">
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="L38" t="n">
         <v>0.01</v>
@@ -3425,7 +3425,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1067.99</v>
+        <v>1079.09</v>
       </c>
       <c r="F39" s="34" t="n">
         <v>0.050033</v>
@@ -3434,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="35" t="n">
-        <v>8470.1</v>
+        <v>8153.8</v>
       </c>
       <c r="I39" t="n">
         <v>5</v>
@@ -3475,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1248.32</v>
+        <v>1257.05</v>
       </c>
       <c r="F40" s="34" t="n">
         <v>0.05004</v>
@@ -3484,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="35" t="n">
-        <v>10866.3</v>
+        <v>10657.9</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1067.99</v>
+        <v>1079.09</v>
       </c>
       <c r="F41" s="34" t="n">
         <v>0.050033</v>
@@ -3534,7 +3534,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="35" t="n">
-        <v>26102.25</v>
+        <v>25534.75</v>
       </c>
       <c r="I41" t="n">
         <v>5</v>
@@ -3575,7 +3575,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F42" s="34" t="n">
         <v>0.050022</v>
@@ -3584,7 +3584,7 @@
         <v>7</v>
       </c>
       <c r="H42" s="35" t="n">
-        <v>53437.51</v>
+        <v>52495.51</v>
       </c>
       <c r="I42" t="n">
         <v>5</v>
@@ -3625,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F43" s="34" t="n">
         <v>0.050022</v>
@@ -3634,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="35" t="n">
-        <v>29031</v>
+        <v>29450.69</v>
       </c>
       <c r="I43" t="n">
         <v>5</v>
@@ -3675,7 +3675,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>9153</v>
+        <v>9273</v>
       </c>
       <c r="F44" s="34" t="n">
         <v>0.050022</v>
@@ -3684,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="35" t="n">
-        <v>7664.23</v>
+        <v>7651.18</v>
       </c>
       <c r="I44" t="n">
         <v>5</v>
@@ -3725,16 +3725,16 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F45" s="34" t="n">
-        <v>0.015007</v>
+        <v>0.015006</v>
       </c>
       <c r="G45" s="35" t="n">
-        <v>82.56</v>
+        <v>84</v>
       </c>
       <c r="H45" s="35" t="n">
-        <v>79732.67999999999</v>
+        <v>78683.2</v>
       </c>
       <c r="I45" t="n">
         <v>5</v>
@@ -3760,7 +3760,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cardano vs US Dollar</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3775,7 +3775,7 @@
         <v>1000</v>
       </c>
       <c r="E46" t="n">
-        <v>915300</v>
+        <v>927300</v>
       </c>
       <c r="F46" s="34" t="n">
         <v>0.006003</v>
@@ -3784,7 +3784,7 @@
         <v>0.0103</v>
       </c>
       <c r="H46" s="35" t="n">
-        <v>0.2305</v>
+        <v>0.2223</v>
       </c>
       <c r="I46" t="n">
         <v>5</v>
@@ -3810,7 +3810,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dogecoin vs US Dollar</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3825,16 +3825,16 @@
         <v>10000</v>
       </c>
       <c r="E47" t="n">
-        <v>9153000</v>
+        <v>9273000</v>
       </c>
       <c r="F47" s="34" t="n">
         <v>0.006003</v>
       </c>
       <c r="G47" s="35" t="n">
-        <v>0.0103</v>
+        <v>0.0102</v>
       </c>
       <c r="H47" s="35" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0939</v>
       </c>
       <c r="I47" t="n">
         <v>5</v>
@@ -3860,7 +3860,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ethereum vs US Dollar</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3875,16 +3875,16 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F48" s="34" t="n">
         <v>0.005002</v>
       </c>
       <c r="G48" s="35" t="n">
-        <v>9.700000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="H48" s="35" t="n">
-        <v>2526.77</v>
+        <v>2494.85</v>
       </c>
       <c r="I48" t="n">
         <v>5</v>
@@ -3910,7 +3910,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Litecoin vs US Dollar</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3925,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>9153</v>
+        <v>9273</v>
       </c>
       <c r="F49" s="34" t="n">
         <v>0.005002</v>
@@ -3934,7 +3934,7 @@
         <v>1.61</v>
       </c>
       <c r="H49" s="35" t="n">
-        <v>53.47</v>
+        <v>55.04</v>
       </c>
       <c r="I49" t="n">
         <v>5</v>
@@ -3960,7 +3960,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solana vs US Dollar</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>100</v>
       </c>
       <c r="E50" t="n">
-        <v>91530</v>
+        <v>92730</v>
       </c>
       <c r="F50" s="34" t="n">
         <v>0.006003</v>
@@ -3984,7 +3984,7 @@
         <v>0.65</v>
       </c>
       <c r="H50" s="35" t="n">
-        <v>96.77</v>
+        <v>103.75</v>
       </c>
       <c r="I50" t="n">
         <v>5</v>
@@ -4025,16 +4025,16 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F51" s="34" t="n">
-        <v>0.250109</v>
+        <v>0.250108</v>
       </c>
       <c r="G51" s="35" t="n">
         <v>0.26</v>
       </c>
       <c r="H51" s="35" t="n">
-        <v>184.86</v>
+        <v>173.63</v>
       </c>
       <c r="I51" t="n">
         <v>5</v>
@@ -4075,16 +4075,16 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F52" s="34" t="n">
-        <v>0.250109</v>
+        <v>0.250108</v>
       </c>
       <c r="G52" s="35" t="n">
         <v>0.06</v>
       </c>
       <c r="H52" s="35" t="n">
-        <v>58.29</v>
+        <v>57.2</v>
       </c>
       <c r="I52" t="n">
         <v>5</v>
@@ -4125,16 +4125,16 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F53" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.100043</v>
       </c>
       <c r="G53" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="H53" s="35" t="n">
-        <v>62.4</v>
+        <v>64.27</v>
       </c>
       <c r="I53" t="n">
         <v>5</v>
@@ -4160,12 +4160,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ETF PowerShares QQQ Trust Series 1 CFD</t>
+          <t>ETF Vanguard Total Bond Market ETF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QQQ.US</t>
+          <t>BND.US</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4175,16 +4175,16 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F54" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.250108</v>
       </c>
       <c r="G54" s="35" t="n">
-        <v>0.53</v>
+        <v>0.26</v>
       </c>
       <c r="H54" s="35" t="n">
-        <v>706.35</v>
+        <v>71.89</v>
       </c>
       <c r="I54" t="n">
         <v>5</v>
@@ -4210,12 +4210,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ETF SPDR Gold Shares CFD</t>
+          <t>ETF Vanguard Total International Bond ETF</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GLD.US</t>
+          <t>BNDX.US</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4225,16 +4225,16 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F55" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.250108</v>
       </c>
       <c r="G55" s="35" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H55" s="35" t="n">
-        <v>428.66</v>
+        <v>47.39</v>
       </c>
       <c r="I55" t="n">
         <v>5</v>
@@ -4260,12 +4260,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ETF SPDR S&amp;P 500 Trust CFD</t>
+          <t>ETF iShares China Large-Cap CFD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SPY.US</t>
+          <t>FXI.US</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4275,16 +4275,16 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F56" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.100043</v>
       </c>
       <c r="G56" s="35" t="n">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
       <c r="H56" s="35" t="n">
-        <v>763.98</v>
+        <v>34.72</v>
       </c>
       <c r="I56" t="n">
         <v>5</v>
@@ -4310,12 +4310,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ETF Vanguard Total Bond Market ETF</t>
+          <t>ETF iShares MSCI Brazil Capped CFD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BND.US</t>
+          <t>EWZ.US</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4325,16 +4325,16 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F57" s="34" t="n">
-        <v>0.250109</v>
+        <v>0.100043</v>
       </c>
       <c r="G57" s="35" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="H57" s="35" t="n">
-        <v>72.48</v>
+        <v>38.25</v>
       </c>
       <c r="I57" t="n">
         <v>5</v>
@@ -4360,12 +4360,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ETF Vanguard Total International Bond ETF</t>
+          <t>ETF iShares MSCI Emerging Markets CFD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BNDX.US</t>
+          <t>EEM.US</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4375,16 +4375,16 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F58" s="34" t="n">
-        <v>0.250109</v>
+        <v>0.100043</v>
       </c>
       <c r="G58" s="35" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H58" s="35" t="n">
-        <v>47.82</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>5</v>
@@ -4410,12 +4410,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ETF iShares China Large-Cap CFD</t>
+          <t>Invesco QQQ Trust (Nasdaq 100)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FXI.US</t>
+          <t>QQQ.US</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -4425,16 +4425,16 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F59" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.100043</v>
       </c>
       <c r="G59" s="35" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H59" s="35" t="n">
-        <v>35.68</v>
+        <v>716.5700000000001</v>
       </c>
       <c r="I59" t="n">
         <v>5</v>
@@ -4460,12 +4460,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ETF iShares MSCI Brazil Capped CFD</t>
+          <t>SPDR Gold Shares</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EWZ.US</t>
+          <t>GLD.US</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -4475,16 +4475,16 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F60" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.100043</v>
       </c>
       <c r="G60" s="35" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H60" s="35" t="n">
-        <v>35.43</v>
+        <v>405.11</v>
       </c>
       <c r="I60" t="n">
         <v>5</v>
@@ -4510,12 +4510,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETF iShares MSCI Emerging Markets CFD</t>
+          <t>SPDR S&amp;P 500 ETF</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EEM.US</t>
+          <t>SPY.US</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4525,16 +4525,16 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F61" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.100043</v>
       </c>
       <c r="G61" s="35" t="n">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="H61" s="35" t="n">
-        <v>66.12</v>
+        <v>763</v>
       </c>
       <c r="I61" t="n">
         <v>5</v>
@@ -4560,12 +4560,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ETF iShares PHLX Semiconductor CFD</t>
+          <t>iShares Russell 2000 (empresas pequeñas)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SOXX.US</t>
+          <t>IWM.US</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -4575,16 +4575,16 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F62" s="34" t="n">
-        <v>0.100044</v>
+        <v>0.250108</v>
       </c>
       <c r="G62" s="35" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="H62" s="35" t="n">
-        <v>502.2</v>
+        <v>291.12</v>
       </c>
       <c r="I62" t="n">
         <v>5</v>
@@ -4610,12 +4610,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ETF iShares Russell 2000 Index Fund</t>
+          <t>iShares Semiconductor ETF (chips)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IWM.US</t>
+          <t>SOXX.US</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4625,16 +4625,16 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F63" s="34" t="n">
-        <v>0.250109</v>
+        <v>0.100043</v>
       </c>
       <c r="G63" s="35" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="H63" s="35" t="n">
-        <v>298.72</v>
+        <v>531.87</v>
       </c>
       <c r="I63" t="n">
         <v>5</v>
@@ -4675,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F64" s="34" t="n">
         <v>0.005002</v>
@@ -4684,7 +4684,7 @@
         <v>0.14</v>
       </c>
       <c r="H64" s="35" t="n">
-        <v>25.61</v>
+        <v>25.23</v>
       </c>
       <c r="I64" t="n">
         <v>5</v>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F65" s="34" t="n">
         <v>0.005002</v>
@@ -4734,7 +4734,7 @@
         <v>0.25</v>
       </c>
       <c r="H65" s="35" t="n">
-        <v>117.07</v>
+        <v>105.89</v>
       </c>
       <c r="I65" t="n">
         <v>5</v>
@@ -4775,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F66" s="34" t="n">
         <v>0.002501</v>
@@ -4784,7 +4784,7 @@
         <v>1.48</v>
       </c>
       <c r="H66" s="35" t="n">
-        <v>278.34</v>
+        <v>258.14</v>
       </c>
       <c r="I66" t="n">
         <v>5</v>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F67" s="34" t="n">
         <v>0.005002</v>
@@ -4834,7 +4834,7 @@
         <v>0.26</v>
       </c>
       <c r="H67" s="35" t="n">
-        <v>456.51</v>
+        <v>523.41</v>
       </c>
       <c r="I67" t="n">
         <v>5</v>
@@ -4875,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F68" s="34" t="n">
         <v>0.020009</v>
@@ -4884,7 +4884,7 @@
         <v>0.6</v>
       </c>
       <c r="H68" s="35" t="n">
-        <v>192.95</v>
+        <v>170.52</v>
       </c>
       <c r="I68" t="n">
         <v>5</v>
@@ -4925,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F69" s="34" t="n">
         <v>0.005002</v>
@@ -4934,7 +4934,7 @@
         <v>0.4</v>
       </c>
       <c r="H69" s="35" t="n">
-        <v>120.23</v>
+        <v>109.96</v>
       </c>
       <c r="I69" t="n">
         <v>5</v>
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F70" s="34" t="n">
         <v>0.002501</v>
@@ -4984,7 +4984,7 @@
         <v>0.35</v>
       </c>
       <c r="H70" s="35" t="n">
-        <v>346.65</v>
+        <v>328.16</v>
       </c>
       <c r="I70" t="n">
         <v>5</v>
@@ -5025,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F71" s="34" t="n">
         <v>0.007503</v>
@@ -5034,7 +5034,7 @@
         <v>0.31</v>
       </c>
       <c r="H71" s="35" t="n">
-        <v>262.57</v>
+        <v>252.3</v>
       </c>
       <c r="I71" t="n">
         <v>5</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F72" s="34" t="n">
         <v>0.005002</v>
@@ -5084,7 +5084,7 @@
         <v>0.05</v>
       </c>
       <c r="H72" s="35" t="n">
-        <v>13.72</v>
+        <v>12.96</v>
       </c>
       <c r="I72" t="n">
         <v>5</v>
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F73" s="34" t="n">
         <v>0.010004</v>
@@ -5134,7 +5134,7 @@
         <v>0.2</v>
       </c>
       <c r="H73" s="35" t="n">
-        <v>120.71</v>
+        <v>124.74</v>
       </c>
       <c r="I73" t="n">
         <v>5</v>
@@ -5175,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F74" s="34" t="n">
         <v>0.002501</v>
@@ -5184,7 +5184,7 @@
         <v>0.31</v>
       </c>
       <c r="H74" s="35" t="n">
-        <v>343.24</v>
+        <v>322.56</v>
       </c>
       <c r="I74" t="n">
         <v>5</v>
@@ -5225,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F75" s="34" t="n">
         <v>0.002501</v>
@@ -5234,7 +5234,7 @@
         <v>0.11</v>
       </c>
       <c r="H75" s="35" t="n">
-        <v>77.7</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="I75" t="n">
         <v>5</v>
@@ -5275,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F76" s="34" t="n">
         <v>0.002501</v>
@@ -5284,7 +5284,7 @@
         <v>0.47</v>
       </c>
       <c r="H76" s="35" t="n">
-        <v>440.38</v>
+        <v>390.97</v>
       </c>
       <c r="I76" t="n">
         <v>5</v>
@@ -5325,7 +5325,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F77" s="34" t="n">
         <v>0.005002</v>
@@ -5334,7 +5334,7 @@
         <v>0.32</v>
       </c>
       <c r="H77" s="35" t="n">
-        <v>313.35</v>
+        <v>312.43</v>
       </c>
       <c r="I77" t="n">
         <v>5</v>
@@ -5375,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F78" s="34" t="n">
         <v>0.002501</v>
@@ -5384,7 +5384,7 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="H78" s="35" t="n">
-        <v>93.48999999999999</v>
+        <v>92.19</v>
       </c>
       <c r="I78" t="n">
         <v>5</v>
@@ -5425,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F79" s="34" t="n">
         <v>0.005002</v>
@@ -5434,7 +5434,7 @@
         <v>0.08</v>
       </c>
       <c r="H79" s="35" t="n">
-        <v>62.55</v>
+        <v>62.71</v>
       </c>
       <c r="I79" t="n">
         <v>5</v>
@@ -5475,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F80" s="34" t="n">
         <v>0.005002</v>
@@ -5484,7 +5484,7 @@
         <v>0.3</v>
       </c>
       <c r="H80" s="35" t="n">
-        <v>26.45</v>
+        <v>24.94</v>
       </c>
       <c r="I80" t="n">
         <v>5</v>
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F81" s="34" t="n">
         <v>0.002501</v>
@@ -5534,7 +5534,7 @@
         <v>0.2</v>
       </c>
       <c r="H81" s="35" t="n">
-        <v>87.77</v>
+        <v>88.92</v>
       </c>
       <c r="I81" t="n">
         <v>5</v>
@@ -5575,16 +5575,16 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F82" s="34" t="n">
-        <v>0.010005</v>
+        <v>0.010004</v>
       </c>
       <c r="G82" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="H82" s="35" t="n">
-        <v>14.51</v>
+        <v>11.15</v>
       </c>
       <c r="I82" t="n">
         <v>5</v>
@@ -5625,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F83" s="34" t="n">
         <v>0.005002</v>
@@ -5634,7 +5634,7 @@
         <v>0.85</v>
       </c>
       <c r="H83" s="35" t="n">
-        <v>215.1</v>
+        <v>212.39</v>
       </c>
       <c r="I83" t="n">
         <v>5</v>
@@ -5675,7 +5675,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F84" s="34" t="n">
         <v>0.005002</v>
@@ -5684,7 +5684,7 @@
         <v>0.89</v>
       </c>
       <c r="H84" s="35" t="n">
-        <v>210.38</v>
+        <v>208.78</v>
       </c>
       <c r="I84" t="n">
         <v>5</v>
@@ -5725,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F85" s="34" t="n">
         <v>0.017508</v>
@@ -5734,7 +5734,7 @@
         <v>2.8</v>
       </c>
       <c r="H85" s="35" t="n">
-        <v>364.13</v>
+        <v>366.34</v>
       </c>
       <c r="I85" t="n">
         <v>5</v>
@@ -5775,16 +5775,16 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F86" s="34" t="n">
-        <v>0.012503</v>
+        <v>0.012501</v>
       </c>
       <c r="G86" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="H86" s="35" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="I86" t="n">
         <v>5</v>
@@ -5825,7 +5825,7 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F87" s="34" t="n">
         <v>0.002501</v>
@@ -5834,7 +5834,7 @@
         <v>0.45</v>
       </c>
       <c r="H87" s="35" t="n">
-        <v>811.3200000000001</v>
+        <v>816.63</v>
       </c>
       <c r="I87" t="n">
         <v>5</v>
@@ -5875,7 +5875,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F88" s="34" t="n">
         <v>0.002501</v>
@@ -5884,7 +5884,7 @@
         <v>0.36</v>
       </c>
       <c r="H88" s="35" t="n">
-        <v>203.33</v>
+        <v>213.63</v>
       </c>
       <c r="I88" t="n">
         <v>5</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F89" s="34" t="n">
         <v>0.005002</v>
@@ -5934,7 +5934,7 @@
         <v>0.14</v>
       </c>
       <c r="H89" s="35" t="n">
-        <v>110.32</v>
+        <v>109.73</v>
       </c>
       <c r="I89" t="n">
         <v>5</v>
@@ -5975,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F90" s="34" t="n">
         <v>0.005002</v>
@@ -5984,7 +5984,7 @@
         <v>0.19</v>
       </c>
       <c r="H90" s="35" t="n">
-        <v>131.66</v>
+        <v>138.18</v>
       </c>
       <c r="I90" t="n">
         <v>5</v>
@@ -6025,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F91" s="34" t="n">
         <v>0.002501</v>
@@ -6034,7 +6034,7 @@
         <v>0.14</v>
       </c>
       <c r="H91" s="35" t="n">
-        <v>92.34</v>
+        <v>88.13</v>
       </c>
       <c r="I91" t="n">
         <v>5</v>
@@ -6075,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F92" s="34" t="n">
         <v>0.017508</v>
@@ -6084,7 +6084,7 @@
         <v>0.2</v>
       </c>
       <c r="H92" s="35" t="n">
-        <v>188.78</v>
+        <v>177.74</v>
       </c>
       <c r="I92" t="n">
         <v>5</v>
@@ -6125,7 +6125,7 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F93" s="34" t="n">
         <v>0.002501</v>
@@ -6134,7 +6134,7 @@
         <v>0.97</v>
       </c>
       <c r="H93" s="35" t="n">
-        <v>965.36</v>
+        <v>900.29</v>
       </c>
       <c r="I93" t="n">
         <v>5</v>
@@ -6175,16 +6175,16 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F94" s="34" t="n">
         <v>0.005002</v>
       </c>
       <c r="G94" s="35" t="n">
-        <v>0.51</v>
+        <v>1.5</v>
       </c>
       <c r="H94" s="35" t="n">
-        <v>378.38</v>
+        <v>376.72</v>
       </c>
       <c r="I94" t="n">
         <v>5</v>
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F95" s="34" t="n">
         <v>0.005002</v>
@@ -6234,7 +6234,7 @@
         <v>0.77</v>
       </c>
       <c r="H95" s="35" t="n">
-        <v>659.26</v>
+        <v>675.8200000000001</v>
       </c>
       <c r="I95" t="n">
         <v>5</v>
@@ -6275,7 +6275,7 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F96" s="34" t="n">
         <v>0.005002</v>
@@ -6284,7 +6284,7 @@
         <v>0.06</v>
       </c>
       <c r="H96" s="35" t="n">
-        <v>435.67</v>
+        <v>540.23</v>
       </c>
       <c r="I96" t="n">
         <v>5</v>
@@ -6325,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F97" s="34" t="n">
         <v>0.005002</v>
@@ -6334,7 +6334,7 @@
         <v>0.11</v>
       </c>
       <c r="H97" s="35" t="n">
-        <v>82.67</v>
+        <v>79.12</v>
       </c>
       <c r="I97" t="n">
         <v>5</v>
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F98" s="34" t="n">
         <v>0.005002</v>
@@ -6384,7 +6384,7 @@
         <v>0.15</v>
       </c>
       <c r="H98" s="35" t="n">
-        <v>106.24</v>
+        <v>104.83</v>
       </c>
       <c r="I98" t="n">
         <v>5</v>
@@ -6425,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F99" s="34" t="n">
         <v>0.007503</v>
@@ -6475,7 +6475,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F100" s="34" t="n">
         <v>0.005002</v>
@@ -6484,7 +6484,7 @@
         <v>0.25</v>
       </c>
       <c r="H100" s="35" t="n">
-        <v>163.88</v>
+        <v>165.03</v>
       </c>
       <c r="I100" t="n">
         <v>5</v>
@@ -6525,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F101" s="34" t="n">
         <v>0.007503</v>
@@ -6534,7 +6534,7 @@
         <v>0.64</v>
       </c>
       <c r="H101" s="35" t="n">
-        <v>327.99</v>
+        <v>309.51</v>
       </c>
       <c r="I101" t="n">
         <v>5</v>
@@ -6575,7 +6575,7 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F102" s="34" t="n">
         <v>0.005002</v>
@@ -6584,7 +6584,7 @@
         <v>0.6</v>
       </c>
       <c r="H102" s="35" t="n">
-        <v>428.76</v>
+        <v>402.93</v>
       </c>
       <c r="I102" t="n">
         <v>5</v>
@@ -6625,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F103" s="34" t="n">
         <v>0.005002</v>
@@ -6634,7 +6634,7 @@
         <v>0.46</v>
       </c>
       <c r="H103" s="35" t="n">
-        <v>211.39</v>
+        <v>204.99</v>
       </c>
       <c r="I103" t="n">
         <v>5</v>
@@ -6675,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F104" s="34" t="n">
         <v>0.005002</v>
@@ -6684,7 +6684,7 @@
         <v>0.08</v>
       </c>
       <c r="H104" s="35" t="n">
-        <v>13.94</v>
+        <v>13.77</v>
       </c>
       <c r="I104" t="n">
         <v>5</v>
@@ -6725,7 +6725,7 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F105" s="34" t="n">
         <v>0.002501</v>
@@ -6734,7 +6734,7 @@
         <v>0.21</v>
       </c>
       <c r="H105" s="35" t="n">
-        <v>344.17</v>
+        <v>324.85</v>
       </c>
       <c r="I105" t="n">
         <v>5</v>
@@ -6775,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F106" s="34" t="n">
         <v>0.002501</v>
@@ -6784,7 +6784,7 @@
         <v>0.08</v>
       </c>
       <c r="H106" s="35" t="n">
-        <v>86.68000000000001</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="I106" t="n">
         <v>5</v>
@@ -6825,7 +6825,7 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F107" s="34" t="n">
         <v>0.002501</v>
@@ -6834,7 +6834,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="H107" s="35" t="n">
-        <v>1032.08</v>
+        <v>1033.05</v>
       </c>
       <c r="I107" t="n">
         <v>5</v>
@@ -6875,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F108" s="34" t="n">
         <v>0.002501</v>
@@ -6884,7 +6884,7 @@
         <v>0.09</v>
       </c>
       <c r="H108" s="35" t="n">
-        <v>34.52</v>
+        <v>37.16</v>
       </c>
       <c r="I108" t="n">
         <v>5</v>
@@ -6925,7 +6925,7 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F109" s="34" t="n">
         <v>0.005002</v>
@@ -6934,7 +6934,7 @@
         <v>0.08</v>
       </c>
       <c r="H109" s="35" t="n">
-        <v>29.08</v>
+        <v>32.07</v>
       </c>
       <c r="I109" t="n">
         <v>5</v>
@@ -6975,7 +6975,7 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F110" s="34" t="n">
         <v>0.005002</v>
@@ -6984,7 +6984,7 @@
         <v>1.6</v>
       </c>
       <c r="H110" s="35" t="n">
-        <v>220.82</v>
+        <v>208.4</v>
       </c>
       <c r="I110" t="n">
         <v>5</v>
@@ -7025,7 +7025,7 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F111" s="34" t="n">
         <v>0.005002</v>
@@ -7034,7 +7034,7 @@
         <v>0.08</v>
       </c>
       <c r="H111" s="35" t="n">
-        <v>86.27</v>
+        <v>106.01</v>
       </c>
       <c r="I111" t="n">
         <v>5</v>
@@ -7075,7 +7075,7 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F112" s="34" t="n">
         <v>0.005002</v>
@@ -7084,7 +7084,7 @@
         <v>0.66</v>
       </c>
       <c r="H112" s="35" t="n">
-        <v>232.46</v>
+        <v>238.26</v>
       </c>
       <c r="I112" t="n">
         <v>5</v>
@@ -7125,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F113" s="34" t="n">
         <v>0.002501</v>
@@ -7134,7 +7134,7 @@
         <v>0.25</v>
       </c>
       <c r="H113" s="35" t="n">
-        <v>356.84</v>
+        <v>354.82</v>
       </c>
       <c r="I113" t="n">
         <v>5</v>
@@ -7175,7 +7175,7 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F114" s="34" t="n">
         <v>0.002501</v>
@@ -7184,7 +7184,7 @@
         <v>0.37</v>
       </c>
       <c r="H114" s="35" t="n">
-        <v>271.04</v>
+        <v>268.83</v>
       </c>
       <c r="I114" t="n">
         <v>5</v>
@@ -7225,7 +7225,7 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F115" s="34" t="n">
         <v>0.002501</v>
@@ -7234,7 +7234,7 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="H115" s="35" t="n">
-        <v>562.84</v>
+        <v>526.27</v>
       </c>
       <c r="I115" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F116" s="34" t="n">
         <v>0.002501</v>
@@ -7284,7 +7284,7 @@
         <v>0.85</v>
       </c>
       <c r="H116" s="35" t="n">
-        <v>597.39</v>
+        <v>569.0599999999999</v>
       </c>
       <c r="I116" t="n">
         <v>5</v>
@@ -7325,7 +7325,7 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F117" s="34" t="n">
         <v>0.005002</v>
@@ -7334,7 +7334,7 @@
         <v>0.72</v>
       </c>
       <c r="H117" s="35" t="n">
-        <v>272.39</v>
+        <v>255.77</v>
       </c>
       <c r="I117" t="n">
         <v>5</v>
@@ -7375,7 +7375,7 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F118" s="34" t="n">
         <v>0.005002</v>
@@ -7384,7 +7384,7 @@
         <v>7</v>
       </c>
       <c r="H118" s="35" t="n">
-        <v>1976.61</v>
+        <v>1876.66</v>
       </c>
       <c r="I118" t="n">
         <v>5</v>
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F119" s="34" t="n">
         <v>0.005002</v>
@@ -7434,7 +7434,7 @@
         <v>0.64</v>
       </c>
       <c r="H119" s="35" t="n">
-        <v>553.22</v>
+        <v>651.74</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -7475,7 +7475,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F120" s="34" t="n">
         <v>0.005002</v>
@@ -7484,7 +7484,7 @@
         <v>0.8</v>
       </c>
       <c r="H120" s="35" t="n">
-        <v>125.94</v>
+        <v>134.89</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -7525,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F121" s="34" t="n">
         <v>0.005002</v>
@@ -7534,7 +7534,7 @@
         <v>0.19</v>
       </c>
       <c r="H121" s="35" t="n">
-        <v>900.79</v>
+        <v>1024.1</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -7575,7 +7575,7 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F122" s="34" t="n">
         <v>0.005002</v>
@@ -7584,7 +7584,7 @@
         <v>0.6</v>
       </c>
       <c r="H122" s="35" t="n">
-        <v>487.84</v>
+        <v>492.91</v>
       </c>
       <c r="I122" t="n">
         <v>5</v>
@@ -7625,7 +7625,7 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F123" s="34" t="n">
         <v>0.005002</v>
@@ -7634,7 +7634,7 @@
         <v>0.14</v>
       </c>
       <c r="H123" s="35" t="n">
-        <v>135.1</v>
+        <v>137.75</v>
       </c>
       <c r="I123" t="n">
         <v>5</v>
@@ -7675,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F124" s="34" t="n">
         <v>0.005002</v>
@@ -7684,7 +7684,7 @@
         <v>0.11</v>
       </c>
       <c r="H124" s="35" t="n">
-        <v>214.93</v>
+        <v>215.78</v>
       </c>
       <c r="I124" t="n">
         <v>5</v>
@@ -7725,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F125" s="34" t="n">
         <v>0.017507</v>
@@ -7734,7 +7734,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H125" s="35" t="n">
-        <v>4.52</v>
+        <v>3.75</v>
       </c>
       <c r="I125" t="n">
         <v>5</v>
@@ -7775,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F126" s="34" t="n">
         <v>0.005002</v>
@@ -7784,7 +7784,7 @@
         <v>0.9</v>
       </c>
       <c r="H126" s="35" t="n">
-        <v>210.12</v>
+        <v>224.54</v>
       </c>
       <c r="I126" t="n">
         <v>5</v>
@@ -7825,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F127" s="34" t="n">
         <v>0.005002</v>
@@ -7834,7 +7834,7 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="H127" s="35" t="n">
-        <v>80.56</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="I127" t="n">
         <v>5</v>
@@ -7875,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F128" s="34" t="n">
         <v>0.002501</v>
@@ -7884,7 +7884,7 @@
         <v>0.35</v>
       </c>
       <c r="H128" s="35" t="n">
-        <v>41.41</v>
+        <v>37.51</v>
       </c>
       <c r="I128" t="n">
         <v>5</v>
@@ -7925,7 +7925,7 @@
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F129" s="34" t="n">
         <v>0.002501</v>
@@ -7934,7 +7934,7 @@
         <v>0.17</v>
       </c>
       <c r="H129" s="35" t="n">
-        <v>142.74</v>
+        <v>163.79</v>
       </c>
       <c r="I129" t="n">
         <v>5</v>
@@ -7975,7 +7975,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F130" s="34" t="n">
         <v>0.005002</v>
@@ -7984,7 +7984,7 @@
         <v>0.19</v>
       </c>
       <c r="H130" s="35" t="n">
-        <v>176.55</v>
+        <v>170.71</v>
       </c>
       <c r="I130" t="n">
         <v>5</v>
@@ -8025,7 +8025,7 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F131" s="34" t="n">
         <v>0.005002</v>
@@ -8034,7 +8034,7 @@
         <v>0.08</v>
       </c>
       <c r="H131" s="35" t="n">
-        <v>27.92</v>
+        <v>27.94</v>
       </c>
       <c r="I131" t="n">
         <v>5</v>
@@ -8075,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F132" s="34" t="n">
         <v>0.002501</v>
@@ -8084,7 +8084,7 @@
         <v>0.31</v>
       </c>
       <c r="H132" s="35" t="n">
-        <v>146.78</v>
+        <v>142.88</v>
       </c>
       <c r="I132" t="n">
         <v>5</v>
@@ -8125,7 +8125,7 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F133" s="34" t="n">
         <v>0.002501</v>
@@ -8134,7 +8134,7 @@
         <v>0.3</v>
       </c>
       <c r="H133" s="35" t="n">
-        <v>157.69</v>
+        <v>176.29</v>
       </c>
       <c r="I133" t="n">
         <v>5</v>
@@ -8175,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F134" s="34" t="n">
         <v>0.002501</v>
@@ -8184,7 +8184,7 @@
         <v>0.47</v>
       </c>
       <c r="H134" s="35" t="n">
-        <v>212.03</v>
+        <v>246.75</v>
       </c>
       <c r="I134" t="n">
         <v>5</v>
@@ -8225,7 +8225,7 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F135" s="34" t="n">
         <v>0.005002</v>
@@ -8234,7 +8234,7 @@
         <v>0.45</v>
       </c>
       <c r="H135" s="35" t="n">
-        <v>219.57</v>
+        <v>206.22</v>
       </c>
       <c r="I135" t="n">
         <v>5</v>
@@ -8275,7 +8275,7 @@
         <v>50</v>
       </c>
       <c r="E136" t="n">
-        <v>45765</v>
+        <v>46365</v>
       </c>
       <c r="F136" s="34" t="n">
         <v>0.020009</v>
@@ -8284,7 +8284,7 @@
         <v>0.23</v>
       </c>
       <c r="H136" s="35" t="n">
-        <v>135.16</v>
+        <v>148.55</v>
       </c>
       <c r="I136" t="n">
         <v>5</v>
@@ -8325,7 +8325,7 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F137" s="34" t="n">
         <v>0.002501</v>
@@ -8334,7 +8334,7 @@
         <v>0.15</v>
       </c>
       <c r="H137" s="35" t="n">
-        <v>106.69</v>
+        <v>101.1</v>
       </c>
       <c r="I137" t="n">
         <v>5</v>
@@ -8375,7 +8375,7 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F138" s="34" t="n">
         <v>0.005002</v>
@@ -8384,7 +8384,7 @@
         <v>0.65</v>
       </c>
       <c r="H138" s="35" t="n">
-        <v>389.91</v>
+        <v>397.21</v>
       </c>
       <c r="I138" t="n">
         <v>5</v>
@@ -8425,7 +8425,7 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F139" s="34" t="n">
         <v>0.002501</v>
@@ -8434,7 +8434,7 @@
         <v>0.59</v>
       </c>
       <c r="H139" s="35" t="n">
-        <v>170.34</v>
+        <v>159.73</v>
       </c>
       <c r="I139" t="n">
         <v>5</v>
@@ -8475,7 +8475,7 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F140" s="34" t="n">
         <v>0.010004</v>
@@ -8484,7 +8484,7 @@
         <v>0.3</v>
       </c>
       <c r="H140" s="35" t="n">
-        <v>358.04</v>
+        <v>368.49</v>
       </c>
       <c r="I140" t="n">
         <v>5</v>
@@ -8525,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F141" s="34" t="n">
         <v>0.005002</v>
@@ -8575,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F142" s="34" t="n">
         <v>0.005002</v>
@@ -8584,7 +8584,7 @@
         <v>0.35</v>
       </c>
       <c r="H142" s="35" t="n">
-        <v>109.06</v>
+        <v>90.16</v>
       </c>
       <c r="I142" t="n">
         <v>5</v>
@@ -8625,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F143" s="34" t="n">
         <v>0.002501</v>
@@ -8634,7 +8634,7 @@
         <v>0.8</v>
       </c>
       <c r="H143" s="35" t="n">
-        <v>338.9</v>
+        <v>311.88</v>
       </c>
       <c r="I143" t="n">
         <v>5</v>
@@ -8675,16 +8675,16 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F144" s="34" t="n">
-        <v>0.005001</v>
+        <v>0.005003</v>
       </c>
       <c r="G144" s="35" t="n">
         <v>0.05</v>
       </c>
       <c r="H144" s="35" t="n">
-        <v>4.71</v>
+        <v>4.27</v>
       </c>
       <c r="I144" t="n">
         <v>5</v>
@@ -8725,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F145" s="34" t="n">
         <v>0.010004</v>
@@ -8734,7 +8734,7 @@
         <v>0.17</v>
       </c>
       <c r="H145" s="35" t="n">
-        <v>79.58</v>
+        <v>71.5</v>
       </c>
       <c r="I145" t="n">
         <v>5</v>
@@ -8775,7 +8775,7 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F146" s="34" t="n">
         <v>0.005002</v>
@@ -8784,7 +8784,7 @@
         <v>0.09</v>
       </c>
       <c r="H146" s="35" t="n">
-        <v>15.2</v>
+        <v>15.44</v>
       </c>
       <c r="I146" t="n">
         <v>5</v>
@@ -8825,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F147" s="34" t="n">
         <v>0.002501</v>
@@ -8834,7 +8834,7 @@
         <v>0.37</v>
       </c>
       <c r="H147" s="35" t="n">
-        <v>381.12</v>
+        <v>367.81</v>
       </c>
       <c r="I147" t="n">
         <v>5</v>
@@ -8875,7 +8875,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F148" s="34" t="n">
         <v>0.002501</v>
@@ -8884,7 +8884,7 @@
         <v>0.28</v>
       </c>
       <c r="H148" s="35" t="n">
-        <v>104.55</v>
+        <v>106.1</v>
       </c>
       <c r="I148" t="n">
         <v>5</v>
@@ -8925,7 +8925,7 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>915.3</v>
+        <v>927.3</v>
       </c>
       <c r="F149" s="34" t="n">
         <v>0.002501</v>
@@ -8934,7 +8934,7 @@
         <v>0.5</v>
       </c>
       <c r="H149" s="35" t="n">
-        <v>110.83</v>
+        <v>104.97</v>
       </c>
       <c r="I149" t="n">
         <v>5</v>
@@ -8960,7 +8960,7 @@
     <row r="151">
       <c r="A151" s="36" t="inlineStr">
         <is>
-          <t>Especificaciones tomadas de la cuenta 51492 de MT5, GrupoInteligenciaSpA-Server, tipo REAL, en CLP, el 2026-08-24 10:45 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días). Los nombres en español son los del catálogo del grupo de análisis; el resto llega con la descripción del broker.</t>
+          <t>Especificaciones tomadas de la cuenta 51492 de MT5, GrupoInteligenciaSpA-Server, tipo REAL, en CLP, el 2026-09-09 15:08 hora Chile. No editar a mano: se regenera con scripts/simulador_gi.py. MODO SWAP 1 = puntos por día por lote; 5 = interés anual sobre el nocional (año de 360 días). Los nombres en español son los del catálogo del grupo de análisis; el resto llega con la descripción del broker.</t>
         </is>
       </c>
     </row>
